--- a/anudeep_lab/LAB2_AINDRILLA.xlsx
+++ b/anudeep_lab/LAB2_AINDRILLA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\anudeep_lab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{905551B8-3086-46F2-93F3-A52D6D6ABFAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A76121A-EECA-41EB-85A6-68EF6398C62D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C8AA18CB-A16A-4424-A6D3-34536EFC64B6}"/>
   </bookViews>
